--- a/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
@@ -2465,7 +2465,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T18:28:48+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T19:19:17+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>

--- a/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
@@ -2465,7 +2465,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T19:19:17+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T19:54:43+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>

--- a/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
@@ -441,18 +441,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX1"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -462,7 +462,7 @@
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="19" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
@@ -480,20 +480,20 @@
     <col width="19" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="44" customWidth="1" min="37" max="37"/>
+    <col width="24" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="27" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="43" max="43"/>
     <col width="23" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="17" customWidth="1" min="46" max="46"/>
     <col width="15" customWidth="1" min="47" max="47"/>
     <col width="18" customWidth="1" min="48" max="48"/>
     <col width="15" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,6 +745,738 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>proj_umusic_hotel_teatro_reina_victor_984a76</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>hotel_pipeline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UMusic Hotel Teatro Reina Victoria</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Plaza de Canalejas</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2027-Q4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>proj_umusic_hotel_teatro_reina_victor_984a76</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>batch_8c1ba6a7e5264098</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:38:37+00:00</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>TBI=20 · views=213</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>proj_edificio_metropolis_984a76</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hotel_pipeline</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Edificio Metropolis</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Calle de Alcala 39</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>proj_edificio_metropolis_984a76</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>batch_8c1ba6a7e5264098</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:38:37+00:00</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>TBI=38 · views=260</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>proj_santa_maría_magdalena_hotel_proj_984a76</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hotel_pipeline</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Santa María Magdalena Hotel Project</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Calle de Hortaleza 88</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>41</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>proj_santa_maría_magdalena_hotel_proj_984a76</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>batch_8c1ba6a7e5264098</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:38:37+00:00</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>TBI=5 · views=107</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proj_nobu_madrid_984a76</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hotel_pipeline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nobu Madrid</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Calle de Alcala 26</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>proj_nobu_madrid_984a76</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>batch_8c1ba6a7e5264098</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:38:37+00:00</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>TBI=38 · views=327</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>proj_el_corte_ingles_hotel_984a76</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hotel_pipeline</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>El Corte Ingles Hotel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Calle de Goya 89</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>111</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>proj_el_corte_ingles_hotel_984a76</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>batch_8c1ba6a7e5264098</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:38:37+00:00</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>TBI=12 · views=149</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>proj_one_shot_canalejas_984a76</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hotel_pipeline</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>One Shot Canalejas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Plaza de Canalejas</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>65</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>New Building</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>proj_one_shot_canalejas_984a76</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>batch_8c1ba6a7e5264098</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:38:37+00:00</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>TBI=8 · views=102</t>
         </is>
       </c>
     </row>
@@ -2465,7 +3197,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T19:54:43+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-14T03:39:19+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>

--- a/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -960,7 +960,7 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1204,7 +1204,7 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1448,7 +1448,7 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3197,7 +3197,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:39:19+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-14T03:50:59+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>

--- a/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_PROYECTOS_MASTER.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -960,7 +960,7 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1204,7 +1204,7 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1448,7 +1448,7 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3197,7 +3197,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:50:59+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-20T00:48:41+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>
